--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082213DB-3E9B-4062-9837-C6D06EBA60F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96BDFFF-5521-43F8-AE17-ED34204DC01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="57">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -221,6 +221,38 @@
   </si>
   <si>
     <t>13:30-15:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐伟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王学恒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>听课</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机网络物理层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机网络概述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12节</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-502a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-505</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -281,7 +313,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -299,6 +331,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1307,7 +1342,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2A24A8-D633-44C1-BBF9-DEBEEE85AC8B}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
@@ -1362,6 +1397,46 @@
         <v>39</v>
       </c>
     </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="1">
+        <v>46269</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="1">
+        <v>46274</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96BDFFF-5521-43F8-AE17-ED34204DC01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671CB424-15E4-4428-BC9D-996A033FD76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -1398,6 +1398,9 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
       <c r="B3" s="1">
         <v>46269</v>
       </c>
@@ -1418,6 +1421,9 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
       <c r="B4" s="1">
         <v>46274</v>
       </c>
